--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26D3B7F9-E974-4FB7-B061-5F0E0FF1FB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7E2934-4436-4ED7-BC78-0BB0BAD78D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Category</t>
   </si>
@@ -65,6 +65,10 @@
   </si>
   <si>
     <t>PP (Polyprophylene)</t>
+  </si>
+  <si>
+    <t>A Type (Standard)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1036,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.796875" customWidth="1"/>
@@ -1122,10 +1126,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1136,9 +1140,20 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>1</v>
       </c>
     </row>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7E2934-4436-4ED7-BC78-0BB0BAD78D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF701BB7-57F1-4584-9DC5-6D9DFC474074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="8832" yWindow="0" windowWidth="14244" windowHeight="12336" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Category</t>
   </si>
@@ -68,6 +68,38 @@
   </si>
   <si>
     <t>A Type (Standard)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mAh/g</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avg.Voltage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>True Density</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>g/cm3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Life</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cycles</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1040,10 +1072,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.796875" customWidth="1"/>
+    <col min="1" max="1" width="16.796875" customWidth="1"/>
     <col min="2" max="2" width="22.296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1157,6 +1189,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF701BB7-57F1-4584-9DC5-6D9DFC474074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0175E973-46FF-4361-9CE5-96444B4318A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8832" yWindow="0" windowWidth="14244" windowHeight="12336" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="5760" yWindow="0" windowWidth="17280" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Category</t>
   </si>
@@ -71,35 +71,19 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Capacity </t>
+    <t>Capacity (mAh/g)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>mAh/g</t>
+    <t>Avg.Voltage (V)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Avg.Voltage</t>
+    <t>True Density (g/cm3)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>V</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>True Density</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>g/cm3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Life</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cycles</t>
+    <t>Base Life (Cycles)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1193,8 +1177,8 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" t="s">
-        <v>17</v>
+      <c r="B11">
+        <v>160</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -1202,10 +1186,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>3.05</v>
       </c>
       <c r="C12">
         <v>3.05</v>
@@ -1213,10 +1197,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>2.2000000000000002</v>
       </c>
       <c r="C13">
         <v>2.2000000000000002</v>
@@ -1224,10 +1208,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>3000</v>
       </c>
       <c r="C14">
         <v>3000</v>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0175E973-46FF-4361-9CE5-96444B4318A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0AD557-EEF0-4EE2-BCC2-06AE6757A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="0" windowWidth="17280" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="8820" yWindow="612" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Category</t>
   </si>
@@ -28,70 +28,77 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Base_Capacity</t>
-  </si>
-  <si>
     <t>Cathode</t>
   </si>
   <si>
-    <t>Prussian White (PW)</t>
-  </si>
-  <si>
-    <t>Polyanion (PI)</t>
-  </si>
-  <si>
-    <t>Layered Oxide (LO)</t>
-  </si>
-  <si>
     <t>Anode</t>
   </si>
   <si>
-    <t>Kurarey A</t>
-  </si>
-  <si>
-    <t>Aekyung Chemical D</t>
-  </si>
-  <si>
     <t>Electrolyte</t>
   </si>
   <si>
-    <t>G Type (Standard)</t>
-  </si>
-  <si>
     <t>Separator</t>
   </si>
   <si>
-    <t>PE (Polyethylene)</t>
-  </si>
-  <si>
-    <t>PP (Polyprophylene)</t>
-  </si>
-  <si>
-    <t>A Type (Standard)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Capacity (mAh/g)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avg.Voltage (V)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>True Density (g/cm3)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Life (Cycles)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Voltage</t>
+  </si>
+  <si>
+    <t>True_Density</t>
+  </si>
+  <si>
+    <t>Base_ICE</t>
+  </si>
+  <si>
+    <t>Rec_Loading</t>
+  </si>
+  <si>
+    <t>Rec_Density</t>
+  </si>
+  <si>
+    <t>Rec_Active</t>
+  </si>
+  <si>
+    <t>Prussian White (Altris)</t>
+  </si>
+  <si>
+    <t>Layered Oxide (HiNa)</t>
+  </si>
+  <si>
+    <t>Polyanion (NVP)</t>
+  </si>
+  <si>
+    <t>Hard Carbon (Kuraray)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Soft Carbon</t>
+  </si>
+  <si>
+    <t>PP/PE (16um)</t>
+  </si>
+  <si>
+    <t>Foil</t>
+  </si>
+  <si>
+    <t>Al Foil (15um)</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>1M NaPF6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +257,12 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -677,8 +690,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,165 +1075,308 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.796875" customWidth="1"/>
-    <col min="2" max="2" width="22.296875" customWidth="1"/>
+    <col min="1" max="1" width="12" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.09765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.69921875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.8984375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>160</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3.05</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F2" s="1">
+        <v>95</v>
+      </c>
+      <c r="G2" s="1">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>94</v>
+      </c>
+      <c r="J2" s="1">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1">
+        <v>135</v>
+      </c>
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E3" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>88</v>
+      </c>
+      <c r="G3" s="1">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1">
+        <v>96</v>
+      </c>
+      <c r="J3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>110</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F4" s="1">
+        <v>92</v>
+      </c>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I4" s="1">
+        <v>92</v>
+      </c>
+      <c r="J4" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1">
+        <v>330</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>92</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>96</v>
+      </c>
+      <c r="J5" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1">
+        <v>280</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="F6" s="1">
+        <v>85</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>96</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>162</v>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>135</v>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="1">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>160</v>
-      </c>
-      <c r="C11">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>3.05</v>
-      </c>
-      <c r="C12">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C13">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>3000</v>
-      </c>
-      <c r="C14">
-        <v>3000</v>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0AD557-EEF0-4EE2-BCC2-06AE6757A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58C171-206C-4B88-BFB7-AE225BCB46ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8820" yWindow="612" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Category</t>
   </si>
@@ -61,44 +61,41 @@
     <t>Rec_Active</t>
   </si>
   <si>
-    <t>Prussian White (Altris)</t>
-  </si>
-  <si>
-    <t>Layered Oxide (HiNa)</t>
-  </si>
-  <si>
-    <t>Polyanion (NVP)</t>
-  </si>
-  <si>
-    <t>Hard Carbon (Kuraray)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Soft Carbon</t>
-  </si>
-  <si>
-    <t>PP/PE (16um)</t>
-  </si>
-  <si>
-    <t>Foil</t>
-  </si>
-  <si>
-    <t>Al Foil (15um)</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
-    <t>1M NaPF6</t>
+    <t>Base_Life</t>
+  </si>
+  <si>
+    <t>Prussian White (PW)</t>
+  </si>
+  <si>
+    <t>Polyanion (PI)</t>
+  </si>
+  <si>
+    <t>Layered Oxide (LO)</t>
+  </si>
+  <si>
+    <t>Kurarey A</t>
+  </si>
+  <si>
+    <t>Aekyung Chemical D</t>
+  </si>
+  <si>
+    <t>G Type (Standard)</t>
+  </si>
+  <si>
+    <t>PE (Polyethylene)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +261,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -446,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -561,6 +565,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -694,11 +713,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1075,23 +1094,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.796875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.8984375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="9.796875" customWidth="1"/>
+    <col min="4" max="4" width="8.09765625" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="9.796875" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" customWidth="1"/>
+    <col min="9" max="9" width="12.69921875" customWidth="1"/>
+    <col min="10" max="10" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1111,272 +1129,264 @@
         <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2">
+        <v>162</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F2" s="2">
+        <v>95</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="J2" s="2">
+        <v>94</v>
+      </c>
+      <c r="K2" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2">
+        <v>135</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F3" s="2">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8000</v>
+      </c>
+      <c r="H3" s="2">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J3" s="2">
+        <v>92</v>
+      </c>
+      <c r="K3" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2">
+        <v>135</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F4" s="2">
+        <v>88</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H4" s="2">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>96</v>
+      </c>
+      <c r="K4" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>340</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J5" s="2">
+        <v>96</v>
+      </c>
+      <c r="K5" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2">
+        <v>310</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2500</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J6" s="2">
+        <v>96</v>
+      </c>
+      <c r="K6" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1">
-        <v>160</v>
-      </c>
-      <c r="D2" s="1">
-        <v>3.05</v>
-      </c>
-      <c r="E2" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F2" s="1">
-        <v>95</v>
-      </c>
-      <c r="G2" s="1">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="I2" s="1">
-        <v>94</v>
-      </c>
-      <c r="J2" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1">
-        <v>135</v>
-      </c>
-      <c r="D3" s="1">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="F3" s="1">
-        <v>88</v>
-      </c>
-      <c r="G3" s="1">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1">
-        <v>96</v>
-      </c>
-      <c r="J3" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1">
-        <v>110</v>
-      </c>
-      <c r="D4" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F4" s="1">
-        <v>92</v>
-      </c>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="I4" s="1">
-        <v>92</v>
-      </c>
-      <c r="J4" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1">
-        <v>330</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="1">
-        <v>92</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I5" s="1">
-        <v>96</v>
-      </c>
-      <c r="J5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1">
-        <v>280</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="F6" s="1">
-        <v>85</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>96</v>
-      </c>
-      <c r="J6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.95</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
         <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58C171-206C-4B88-BFB7-AE225BCB46ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E18F1B-555C-4082-B11A-45100314B580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>Category</t>
   </si>
@@ -40,18 +40,6 @@
     <t>Separator</t>
   </si>
   <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Voltage</t>
-  </si>
-  <si>
-    <t>True_Density</t>
-  </si>
-  <si>
-    <t>Base_ICE</t>
-  </si>
-  <si>
     <t>Rec_Loading</t>
   </si>
   <si>
@@ -64,12 +52,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Base_Life</t>
-  </si>
-  <si>
     <t>Prussian White (PW)</t>
   </si>
   <si>
@@ -89,6 +71,21 @@
   </si>
   <si>
     <t>PE (Polyethylene)</t>
+  </si>
+  <si>
+    <t>Base_Capacity (mAh/g)</t>
+  </si>
+  <si>
+    <t>Base_Avg.Voltage (V)</t>
+  </si>
+  <si>
+    <t>Base_True Density (g/cm3)</t>
+  </si>
+  <si>
+    <t>Base_Life (Cycles)</t>
+  </si>
+  <si>
+    <t>Base_ICE (%)</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1109,7 +1106,7 @@
     <col min="10" max="10" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,39 +1114,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>162</v>
@@ -1161,30 +1155,27 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F2" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G2" s="2">
         <v>95</v>
       </c>
-      <c r="G2" s="2">
-        <v>4000</v>
-      </c>
       <c r="H2" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J2" s="2">
-        <v>94</v>
-      </c>
-      <c r="K2" s="2">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2">
         <v>135</v>
@@ -1196,10 +1187,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F3" s="2">
+        <v>8000</v>
+      </c>
+      <c r="G3" s="2">
         <v>92</v>
-      </c>
-      <c r="G3" s="2">
-        <v>8000</v>
       </c>
       <c r="H3" s="2">
         <v>12</v>
@@ -1208,18 +1199,15 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J3" s="2">
-        <v>92</v>
-      </c>
-      <c r="K3" s="2">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
         <v>135</v>
@@ -1231,10 +1219,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G4" s="2">
         <v>88</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3000</v>
       </c>
       <c r="H4" s="2">
         <v>15</v>
@@ -1243,18 +1231,15 @@
         <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>96</v>
-      </c>
-      <c r="K4" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>340</v>
@@ -1266,30 +1251,27 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G5" s="2">
         <v>92</v>
       </c>
-      <c r="G5" s="2">
-        <v>3000</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>96</v>
-      </c>
-      <c r="K5" s="2">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>310</v>
@@ -1301,30 +1283,27 @@
         <v>1.5</v>
       </c>
       <c r="F6" s="2">
+        <v>2500</v>
+      </c>
+      <c r="G6" s="2">
         <v>90</v>
       </c>
-      <c r="G6" s="2">
-        <v>2500</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>96</v>
-      </c>
-      <c r="K6" s="2">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1350,16 +1329,13 @@
       <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="2">
-        <v>25</v>
-      </c>
     </row>
-    <row r="8" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1384,9 +1360,6 @@
       </c>
       <c r="J8" s="2">
         <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E18F1B-555C-4082-B11A-45100314B580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E49BCC8-CA91-4EEF-8A73-21D2F3E04F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Category</t>
   </si>
@@ -58,34 +58,28 @@
     <t>Polyanion (PI)</t>
   </si>
   <si>
-    <t>Layered Oxide (LO)</t>
-  </si>
-  <si>
-    <t>Kurarey A</t>
-  </si>
-  <si>
-    <t>Aekyung Chemical D</t>
-  </si>
-  <si>
-    <t>G Type (Standard)</t>
-  </si>
-  <si>
-    <t>PE (Polyethylene)</t>
-  </si>
-  <si>
-    <t>Base_Capacity (mAh/g)</t>
-  </si>
-  <si>
-    <t>Base_Avg.Voltage (V)</t>
-  </si>
-  <si>
-    <t>Base_True Density (g/cm3)</t>
-  </si>
-  <si>
-    <t>Base_Life (Cycles)</t>
-  </si>
-  <si>
-    <t>Base_ICE (%)</t>
+    <t>Base_Capacity</t>
+  </si>
+  <si>
+    <t>Base_Avg_Voltage</t>
+  </si>
+  <si>
+    <t>Base_True_Density</t>
+  </si>
+  <si>
+    <t>Base_Life</t>
+  </si>
+  <si>
+    <t>Base_ICE</t>
+  </si>
+  <si>
+    <t>Hard Carbon (HC)</t>
+  </si>
+  <si>
+    <t>Standard (NaPF6)</t>
+  </si>
+  <si>
+    <t>PE (16um)</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1114,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1161,13 +1155,13 @@
         <v>95</v>
       </c>
       <c r="H2" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
         <v>2.5</v>
       </c>
       <c r="J2" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -1178,10 +1172,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D3" s="2">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="E3" s="2">
         <v>2.2000000000000002</v>
@@ -1204,162 +1198,98 @@
     </row>
     <row r="4" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="D4" s="2">
-        <v>3.05</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="2">
-        <v>2.2000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="2">
         <v>3000</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2">
-        <v>15</v>
+        <v>92</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="I4" s="2">
-        <v>3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J4" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.2</v>
       </c>
       <c r="F5" s="2">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>95</v>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="2">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.95</v>
       </c>
       <c r="F6" s="2">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
+      <c r="I6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E49BCC8-CA91-4EEF-8A73-21D2F3E04F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB03D70-4A79-4329-A312-7BF438619CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Category</t>
   </si>
@@ -73,13 +73,19 @@
     <t>Base_ICE</t>
   </si>
   <si>
-    <t>Hard Carbon (HC)</t>
-  </si>
-  <si>
     <t>Standard (NaPF6)</t>
   </si>
   <si>
     <t>PE (16um)</t>
+  </si>
+  <si>
+    <t>Layered Oxide (LO)</t>
+  </si>
+  <si>
+    <t>Aekyung Chemical (AK)</t>
+  </si>
+  <si>
+    <t>Kuraray (KU)</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1140,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="2">
         <v>3.05</v>
@@ -1198,97 +1204,161 @@
     </row>
     <row r="4" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2">
+        <v>135</v>
+      </c>
+      <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2">
-        <v>330</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.1</v>
-      </c>
       <c r="E4" s="2">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F4" s="2">
         <v>3000</v>
       </c>
       <c r="G4" s="2">
-        <v>92</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="H4" s="2">
+        <v>15</v>
       </c>
       <c r="I4" s="2">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1.2</v>
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.5</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>9</v>
+      <c r="I5" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J5" s="2">
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.95</v>
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.5</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J6" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
     </row>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB03D70-4A79-4329-A312-7BF438619CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA6D0D6-E9C8-4F19-A024-A51C4A6DA39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Category</t>
   </si>
@@ -82,10 +82,13 @@
     <t>Layered Oxide (LO)</t>
   </si>
   <si>
-    <t>Aekyung Chemical (AK)</t>
-  </si>
-  <si>
-    <t>Kuraray (KU)</t>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Kurarey A</t>
+  </si>
+  <si>
+    <t>Aekyung Chemical D</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1106,7 +1109,7 @@
     <col min="10" max="10" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="42" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1137,8 +1140,11 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D2" s="2">
         <v>3.05</v>
@@ -1169,8 +1175,11 @@
       <c r="J2" s="2">
         <v>92</v>
       </c>
+      <c r="K2" s="2">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1178,10 +1187,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D3" s="2">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="E3" s="2">
         <v>2.2000000000000002</v>
@@ -1201,8 +1210,11 @@
       <c r="J3" s="2">
         <v>90</v>
       </c>
+      <c r="K3" s="2">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1213,10 +1225,10 @@
         <v>135</v>
       </c>
       <c r="D4" s="2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E4" s="2">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F4" s="2">
         <v>3000</v>
@@ -1233,28 +1245,31 @@
       <c r="J4" s="2">
         <v>96</v>
       </c>
+      <c r="K4" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="2">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="D5" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E5" s="2">
         <v>1.5</v>
       </c>
       <c r="F5" s="2">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G5" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>9</v>
@@ -1263,30 +1278,33 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="J5" s="2">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="K5" s="2">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="2">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="D6" s="2">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E6" s="2">
         <v>1.5</v>
       </c>
       <c r="F6" s="2">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
@@ -1295,10 +1313,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="J6" s="2">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="K6" s="2">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>

--- a/material_list.xlsx
+++ b/material_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA6D0D6-E9C8-4F19-A024-A51C4A6DA39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D24C1F-4938-4A2B-B97F-490644A1A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
+    <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{C26724A0-0135-4B91-BBF4-0E026F4789EF}"/>
   </bookViews>
   <sheets>
     <sheet name="material_list" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Category</t>
   </si>
@@ -34,61 +34,28 @@
     <t>Anode</t>
   </si>
   <si>
-    <t>Electrolyte</t>
-  </si>
-  <si>
-    <t>Separator</t>
-  </si>
-  <si>
     <t>Rec_Loading</t>
   </si>
   <si>
-    <t>Rec_Density</t>
+    <t>Capacity</t>
   </si>
   <si>
-    <t>Rec_Active</t>
+    <t>Voltage</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Density</t>
   </si>
   <si>
-    <t>Prussian White (PW)</t>
+    <t>Life</t>
   </si>
   <si>
-    <t>Polyanion (PI)</t>
+    <t>Prussian White</t>
   </si>
   <si>
-    <t>Base_Capacity</t>
+    <t>Layered Oxide</t>
   </si>
   <si>
-    <t>Base_Avg_Voltage</t>
-  </si>
-  <si>
-    <t>Base_True_Density</t>
-  </si>
-  <si>
-    <t>Base_Life</t>
-  </si>
-  <si>
-    <t>Base_ICE</t>
-  </si>
-  <si>
-    <t>Standard (NaPF6)</t>
-  </si>
-  <si>
-    <t>PE (16um)</t>
-  </si>
-  <si>
-    <t>Layered Oxide (LO)</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Kurarey A</t>
-  </si>
-  <si>
-    <t>Aekyung Chemical D</t>
+    <t>Hard Carbon (A)</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4568C6-5864-49C4-A0C1-4368FBDBE8BB}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1109,7 +1076,7 @@
     <col min="10" max="10" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="42" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,39 +1084,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
         <v>162</v>
@@ -1164,223 +1119,53 @@
         <v>4000</v>
       </c>
       <c r="G2" s="2">
-        <v>95</v>
-      </c>
-      <c r="H2" s="2">
         <v>14</v>
       </c>
-      <c r="I2" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="J2" s="2">
-        <v>92</v>
-      </c>
-      <c r="K2" s="2">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>140</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2">
-        <v>135</v>
-      </c>
-      <c r="D3" s="2">
-        <v>3.05</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F3" s="2">
-        <v>8000</v>
-      </c>
-      <c r="G3" s="2">
-        <v>92</v>
-      </c>
-      <c r="H3" s="2">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J3" s="2">
-        <v>90</v>
-      </c>
-      <c r="K3" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C4" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="D4" s="2">
-        <v>3.05</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="2">
-        <v>2.2000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="2">
         <v>3000</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2">
-        <v>15</v>
-      </c>
-      <c r="I4" s="2">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>96</v>
-      </c>
-      <c r="K4" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2">
-        <v>340</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3000</v>
-      </c>
-      <c r="G5" s="2">
-        <v>92</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J5" s="2">
-        <v>96</v>
-      </c>
-      <c r="K5" s="2">
         <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2">
-        <v>310</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2500</v>
-      </c>
-      <c r="G6" s="2">
-        <v>90</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J6" s="2">
-        <v>96</v>
-      </c>
-      <c r="K6" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
